--- a/examples/sample_basic.xlsx
+++ b/examples/sample_basic.xlsx
@@ -413,21 +413,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>sample_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>gold_label</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>model_output</t>
         </is>
@@ -436,62 +441,82 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>7651543994911984905</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>S001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>target_a</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>{"prob_1": 0.92, "prob_2": 0.08, "reason": "示例说明A"}</t>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>{"prob_1": 0.92, "prob_2": 0.08, "reason": "示例说明A", "items": ["item_a", "item_b"]}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>7651543994911984906</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>S002</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>target_b</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>{"prob_1": 0.37, "prob_2": 0.63, "reason": "示例说明B"}</t>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>{"prob_1": 0.37, "prob_2": 0.63, "reason": "示例说明B", "items": ["item_c"]}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>7651543994911984907</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>S003</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>target_a</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>7651543994911984908</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>S004</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>target_b</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>运行失败</t>
         </is>
